--- a/REVISION_CLINICA/revision_clinica.xlsx
+++ b/REVISION_CLINICA/revision_clinica.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LEEME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Prioridad (riesgo letal)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Bioestadística" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cardiología" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cirugía y Trauma" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Dermatología" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Endocrinología" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gastroenterología" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Ginecología" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Infectología" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Inglés técnico" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Medicina Interna" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Medicina Preventiva" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Neurología" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Obstetricia" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Oftalmología" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Otorrinolaringología" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Pediatría" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Psiquiatría" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Correcciones" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Resumen" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEEME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prioridad (riesgo letal)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bioestadística" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cardiología" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cirugía y Trauma" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dermatología" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endocrinología" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gastroenterología" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ginecología" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Infectología" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inglés técnico" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medicina Interna" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medicina Preventiva" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neurología" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obstetricia" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oftalmología" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Otorrinolaringología" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pediatría" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Psiquiatría" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correcciones" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prioridad (riesgo letal)'!$A$1:$N$64</definedName>
@@ -835,9 +835,21 @@
           <t>IDSA, Practice Guidelines for Bacterial Meningitis (Tunkel et al., Clin Infect Dis 2004); ESCMID Guideline 2016</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>IDSA 2004 (doi:10.1086/425368) y ESCMID 2016 (doi:10.1016/j.cmi.2016.01.007) localizadas sin resumen</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1047,9 +1059,21 @@
           <t>Surviving Sepsis Campaign 2021</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>SSC 2021 (doi:10.1007/s00134-021-06506-y): antimicrobiano en 1 h; cultivos sin retrasarlo</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1207,9 +1231,21 @@
           <t>CDC, guías de tratamiento de ITS 2021</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>CDC 2021 (doi:10.15585/mmwr.rr7004a1) localizada</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1901,9 +1937,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1957,9 +2001,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -2013,9 +2065,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -2069,9 +2129,21 @@
           <t>GINA 2024; estudio SMART</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>SMART (doi:10.1378/chest.129.1.15): más muertes por asma con salmeterol</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -2229,9 +2301,17 @@
           <t>GINA (betabloqueadores no selectivos como desencadenante de broncoespasmo)</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -2753,9 +2833,17 @@
           <t>ACC/AHA, Guideline for High Blood Pressure in Adults (2017)</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2809,9 +2897,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2865,9 +2961,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2921,9 +3025,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2977,9 +3089,17 @@
           <t>ESC 2019, guía de embolia pulmonar</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -3612,9 +3732,21 @@
           <t>OMS, Rabies Vaccines: Position Paper (2018); NOM-011-SSA2-2011</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>ACIP 2008 (PMID 18496505) localizada; MMWR 2026: murciélago es la principal fuente de rabia humana en EE. UU.</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -3668,9 +3800,21 @@
           <t>OMS, Rabies Vaccines: Position Paper (2018); NOM-011-SSA2-2011</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>ACIP 2008 localizada</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -3991,9 +4135,21 @@
           <t>AHA/ASA, Guidelines for the Management of Aneurysmal SAH (2012)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>AHA/ASA 2023 (doi:10.1161/STR.0000000000000436) localizada; vía oral no confirmada en resumen</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -4096,12 +4252,24 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>AHA/ASA 2019, manejo temprano del EVC isquémico</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>AHA/ASA 2019, Powers WJ et al., Stroke 2019 (doi:10.1161/STR.0000000000000211); Zinkstok SM et al., ARTIS, Lancet 2012 (doi:10.1016/S0140-6736(12)60949-0)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente: se añade ARTIS (doi:10.1016/S0140-6736(12)60949-0). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -4578,9 +4746,21 @@
           <t>ACOG Practice Bulletin 200: Early Pregnancy Loss (2018)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>ACOG PB 200 (doi:10.1097/AOG.0000000000002899) sin mención de infección en el resumen</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -4631,12 +4811,24 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Medscape, manejo del desprendimiento de placenta</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>Towers CV et al., Is tocolysis safe in the management of third-trimester bleeding?, Am J Obstet Gynecol 1999 (doi:10.1016/s0002-9378(99)70053-0); Hladky K et al., Placental Abruption, Obstet Gynecol Surv 2002</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente (Medscape no es fuente primaria). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -4890,17 +5082,29 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Castillo: La inestabilidad hemodinámica o el hemoperitoneo contraindican en forma absoluta el metotrexato y obligan a cirugía.</t>
+          <t>Castillo: La inestabilidad hemodinámica o los datos de rotura contraindican el metotrexato y obligan a cirugía.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>ACOG Practice Bulletin 193</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>ACOG Practice Bulletin 193: Tubal Ectopic Pregnancy, Obstet Gynecol 2018 (doi:10.1097/AOG.0000000000002560)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>El hemoperitoneo por sí solo no es contraindicación absoluta; sí la inestabilidad o la rotura (ACOG PB 193). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -5211,12 +5415,24 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Medscape, manejo del desprendimiento de placenta</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>Towers CV et al., Is tocolysis safe in the management of third-trimester bleeding?, Am J Obstet Gynecol 1999 (doi:10.1016/s0002-9378(99)70053-0); Hladky K et al., Placental Abruption, Obstet Gynecol Surv 2002</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente (Medscape no es fuente primaria). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -5322,9 +5538,21 @@
           <t>OMS, uterotónicos para la prevención de HPP; ficha técnica de ergometrina</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>FIGO 2022 (doi:10.1002/ijgo.14116): oxitocina primera línea; ergot tras excluir hipertensión</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -5430,9 +5658,21 @@
           <t>FIGO 2022, recomendaciones de manejo de la HPP</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>FIGO 2022: definición clásica &gt;500 mL vaginal, &gt;1000 mL cesárea</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -5538,9 +5778,21 @@
           <t>Farmacología de agonistas beta-2 (relajan el útero); la hemorragia materna con inestabilidad contraindica los tocolíticos</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient data: sin fuente específica localizada; el mecanismo (tocolítico) es farmacología básica</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -5698,9 +5950,21 @@
           <t>FIGO, recomendaciones de buena práctica en parto pretérmino; contraindicación absoluta de tocólisis en infección intraamniótica</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient data: fuente no localizada en PubMed</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -5962,9 +6226,21 @@
           <t>ACOG Practice Bulletin 222: Gestational Hypertension and Preeclampsia (2020)</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>ACOG PB 222 no localizada en PubMed</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -7651,9 +7927,21 @@
           <t>CDC/ACIP, Prevention of Measles, Rubella, CRS, and Mumps (MMWR 2013)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>ACIP 2013 (PMID 23760231): evitar el embarazo tras vacuna con rubéola</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -7915,9 +8203,21 @@
           <t>OMS/AIEPI, Plan C</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Plan C OMS/AIEPI no indexado</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -8231,9 +8531,21 @@
           <t>OMS/AIEPI, Plan C</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Plan C OMS/AIEPI no indexado</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -8599,9 +8911,21 @@
           <t>AHA/AAP, Neonatal Resuscitation Program, 8a ed. (2021)</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>AHA 2020 (doi:10.1161/CIR.0000000000000902) localizada</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -8707,9 +9031,21 @@
           <t>AHA/AAP, Neonatal Resuscitation Program, 8a ed. (2021)</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>IV 0.01-0.03 mg/kg (Ramsie 2024, doi:10.1159/000535502; ILCOR)</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -8763,9 +9099,21 @@
           <t>AHA/AAP, Neonatal Resuscitation Program, 8a ed. (2021)</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>FC &lt;60 tras 30 s de ventilación (ILCOR; Ramachandran 2022)</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -9027,9 +9375,21 @@
           <t>AAP, Clinical Report: Hypertrophic Pyloric Stenosis; Hernanz-Schulman, Radiology (2003)</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>La fuente citada ('AAP Clinical Report') no se localizó; Insufficient data</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -10026,9 +10386,21 @@
           <t>APA, Practice Guideline for the Assessment and Treatment of Patients with Suicidal Behaviors (2010)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>APA 2010 no localizada en PubMed</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -10079,12 +10451,24 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>NICE NG225, Self-harm: assessment, management and preventing recurrence (2022)</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>NICE NG225 (2022); Steeg S et al., Accuracy of risk scales for predicting repeat self-harm and suicide, BMC Psychiatry 2018 (doi:10.1186/s12888-018-1693-z): AUC 51% para SAD PERSONS</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente: Steeg 2018 (AUC 51%). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -10138,9 +10522,21 @@
           <t>CANMAT/ISBD, Guidelines for the Management of Patients with Bipolar Disorder (2018)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>CANMAT/ISBD localizada (doi:10.1111/bdi.13135)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -10290,17 +10686,29 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Navarro: Tras un síndrome neuroléptico maligno se espera al menos 2 semanas antes de reintroducir un antipsicótico, con una dosis baja y vigilancia estrecha.</t>
+          <t>Navarro: Tras un síndrome neuroléptico maligno el antipsicótico se reintroduce solo después de un periodo sin fármaco (suele recomendarse al menos 2 semanas), de preferencia con otro agente, a dosis baja y con vigilancia estrecha.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Treatment of Patients with Schizophrenia (2020); Strawn et al., Am J Psychiatry (2007)</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>Pileggi DJ, Cook AM, Neuroleptic Malignant Syndrome, Ann Pharmacother 2016 (doi:10.1177/1060028016657553); Strawn JR et al., Am J Psychiatry 2007 (doi:10.1176/ajp.2007.164.6.870)</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Periodo sin fármaco y cambio de agente (Pileggi 2016); '2 semanas' queda como 'suele recomendarse'. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -10510,9 +10918,21 @@
           <t>APA, Practice Guideline for the Treatment of Patients with Schizophrenia (2020)</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>APA 2020 no localizada en PubMed</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N13"/>
@@ -10669,17 +11089,29 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Navarro: En el infarto con choque cardiogénico la reperfusión de elección es la ICP, sin importar el tiempo de retraso. La fibrinólisis queda como último recurso.</t>
+          <t>Navarro: En el infarto con choque cardiogénico la reperfusión de elección es la ICP inmediata. La fibrinólisis solo se considera si la ICP no puede hacerse a tiempo.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017); ESC Guidelines on ACS (2023)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Samsky MD et al., Cardiogenic Shock After Acute Myocardial Infarction: A Review, JAMA 2021 (doi:10.1001/jama.2021.18323); Thiele H et al., CULPRIT-SHOCK, NEJM 2017 (doi:10.1056/NEJMoa1710261)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Comentario: ICP inmediata; fibrinólisis solo si la ICP no llega a tiempo. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -10733,9 +11165,17 @@
           <t>ESC Guidelines on ACS (2023); ACC/AHA STEMI (2013)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -10789,9 +11229,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -10837,17 +11285,29 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Mendoza: La meta es una ICP primaria en 90 minutos o menos desde el primer contacto médico; si no se logra, se considera fibrinólisis.</t>
+          <t>Mendoza: La ICP primaria se hace lo antes posible; si no puede realizarse dentro de los 120 minutos siguientes al diagnóstico, se administra fibrinólisis.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>Bhatt DL et al., Diagnosis and Treatment of Acute Coronary Syndromes: A Review, JAMA 2022 (doi:10.1001/jama.2022.0358); Vogel B et al., Nat Rev Dis Primers 2019 (doi:10.1038/s41572-019-0090-3)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Comentario: umbral de 120 min desde el diagnóstico, no 90 min desde el primer contacto. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -10901,9 +11361,21 @@
           <t>ATLS 10a ed., Capítulo 3 (Choque) y Capítulo 4 (Trauma torácico)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. es un libro, no indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -10957,9 +11429,21 @@
           <t>ATLS 10a ed., Capítulo 3 (Choque obstructivo) y Capítulo 4</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. es un libro, no indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -11013,9 +11497,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis (J Hepatobiliary Pancreat Sci 2018)</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>TG18 (doi:10.1002/jhbp.509): drenaje biliar en colangitis moderada/grave</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -11069,9 +11565,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>TG18: tratamiento inmediato sin esperar diagnóstico definitivo; SSC 2021: antimicrobiano en 1 h</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -11125,9 +11633,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>TG18 (doi:10.1002/jhbp.509)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -11181,9 +11701,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis (J Hepatobiliary Pancreat Sci 2018)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>TG18 (doi:10.1002/jhbp.509): drenaje biliar en colangitis moderada/grave</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -11237,9 +11769,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>TG18: tratamiento inmediato sin esperar diagnóstico definitivo; SSC 2021: antimicrobiano en 1 h</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -11293,9 +11837,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>TG18 (doi:10.1002/jhbp.509)</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -11346,12 +11902,24 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>WSES, Management of Adhesive Small Bowel Obstruction Guidelines (2017)</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>Ponte CD, Nappi JM, Review of a new gastrointestinal drug: metoclopramide, Am J Hosp Pharm 1981 (doi:10.1093/ajhp/38.6.829): contraindicada en obstrucción, hemorragia o perforación gastrointestinal; ficha técnica</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente (la citada no trata metoclopramida). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -11405,9 +11973,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulo 3</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. no indexado</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -11461,9 +12041,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulos 3 y 4</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. no indexado</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -11517,9 +12109,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulo 3</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. no indexado</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -11573,9 +12177,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulos 3 y 4</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. es un libro, no indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -11629,9 +12245,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulos 3 y 4</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. es un libro, no indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -11685,9 +12313,21 @@
           <t>ADA, Hyperglycemic Crises in Adults with Diabetes: A Consensus Report (2024)</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>ADA 2024 (doi:10.2337/dci24-0032) localizada; texto confirmado en JBDS: insulina fija hasta resolver la cetosis y glucosa al bajar</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -11741,9 +12381,21 @@
           <t>ASCRS, Clinical Practice Guidelines for Left-Sided Colonic Diverticulitis (2020)</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>ASCRS 2020 (doi:10.1097/DCR.0000000000001679) sin resumen</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -11797,9 +12449,21 @@
           <t>ESVS, Guidelines on the Management of Diseases of Mesenteric Arteries (2017); WSES (2022)</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2022 (doi:10.1186/s13017-022-00443-x): heparina temprana mejora la supervivencia</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -11853,9 +12517,21 @@
           <t>WSES, Acute Mesenteric Ischemia Guidelines (2022)</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2022: vasopresores con cautela; eliminarlos es medida primaria</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -11909,9 +12585,21 @@
           <t>WSES, Acute Mesenteric Ischemia Guidelines (2022)</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2022</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -11957,17 +12645,29 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Navarro: La estrategia es restrictiva, con umbral de 7 g/dL y meta de 7 a 9. Sobretransfundir eleva la presión portal y favorece el resangrado.</t>
+          <t>Navarro: La estrategia es restrictiva: se transfunde con hemoglobina cercana a 7 g/dL y la meta es de 7 a 8 g/dL. Sobretransfundir eleva la presión portal y favorece el resangrado.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Baveno VII Consensus (J Hepatol 2022); AASLD Guidance on Portal Hypertensive Bleeding (2017)</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>Baveno VII, J Hepatol 2022 (doi:10.1016/j.jhep.2021.12.022), recomendación 6.2; Villanueva C et al., NEJM 2013 (doi:10.1056/NEJMoa1211801)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Meta 7-8 g/dL (Baveno VII 6.2), no 7-9. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -12021,9 +12721,21 @@
           <t>Baveno VII Consensus (J Hepatol 2022)</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Baveno VII 7.7: reducir o suspender BBNS con PAS &lt;90 o PAM &lt;65</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -12077,9 +12789,21 @@
           <t>IDSA, Practice Guidelines for Bacterial Meningitis (Tunkel et al., Clin Infect Dis 2004); ESCMID Guideline 2016</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>IDSA 2004 (doi:10.1086/425368) y ESCMID 2016 (doi:10.1016/j.cmi.2016.01.007) localizadas sin resumen</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -12133,9 +12857,21 @@
           <t>Surviving Sepsis Campaign 2021</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>SSC 2021 (doi:10.1007/s00134-021-06506-y): antimicrobiano en 1 h; cultivos sin retrasarlo</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -12189,9 +12925,21 @@
           <t>CDC, guías de tratamiento de ITS 2021</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>CDC 2021 (doi:10.15585/mmwr.rr7004a1) localizada</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -12245,9 +12993,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -12301,9 +13057,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -12357,9 +13121,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -12413,9 +13185,21 @@
           <t>GINA 2024; estudio SMART</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>SMART (doi:10.1378/chest.129.1.15): más muertes por asma con salmeterol</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -12469,9 +13253,17 @@
           <t>GINA (betabloqueadores no selectivos como desencadenante de broncoespasmo)</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -12525,9 +13317,17 @@
           <t>ACC/AHA, Guideline for High Blood Pressure in Adults (2017)</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -12581,9 +13381,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -12637,9 +13445,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -12693,9 +13509,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -12749,9 +13573,17 @@
           <t>ESC 2019, guía de embolia pulmonar</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -12805,9 +13637,21 @@
           <t>OMS, Rabies Vaccines: Position Paper (2018); NOM-011-SSA2-2011</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>ACIP 2008 (PMID 18496505) localizada; MMWR 2026: murciélago es la principal fuente de rabia humana en EE. UU.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -12861,9 +13705,21 @@
           <t>OMS, Rabies Vaccines: Position Paper (2018); NOM-011-SSA2-2011</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>ACIP 2008 localizada</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -12917,9 +13773,21 @@
           <t>AHA/ASA, Guidelines for the Management of Aneurysmal SAH (2012)</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>AHA/ASA 2023 (doi:10.1161/STR.0000000000000436) localizada; vía oral no confirmada en resumen</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -12970,12 +13838,24 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>AHA/ASA 2019, manejo temprano del EVC isquémico</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>AHA/ASA 2019, Powers WJ et al., Stroke 2019 (doi:10.1161/STR.0000000000000211); Zinkstok SM et al., ARTIS, Lancet 2012 (doi:10.1016/S0140-6736(12)60949-0)</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente: se añade ARTIS (doi:10.1016/S0140-6736(12)60949-0). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -13029,9 +13909,21 @@
           <t>ACOG Practice Bulletin 200: Early Pregnancy Loss (2018)</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>ACOG PB 200 (doi:10.1097/AOG.0000000000002899) sin mención de infección en el resumen</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -13082,12 +13974,24 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Medscape, manejo del desprendimiento de placenta</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>Towers CV et al., Is tocolysis safe in the management of third-trimester bleeding?, Am J Obstet Gynecol 1999 (doi:10.1016/s0002-9378(99)70053-0); Hladky K et al., Placental Abruption, Obstet Gynecol Surv 2002</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente (Medscape no es fuente primaria). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -13133,17 +14037,29 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Castillo: La inestabilidad hemodinámica o el hemoperitoneo contraindican en forma absoluta el metotrexato y obligan a cirugía.</t>
+          <t>Castillo: La inestabilidad hemodinámica o los datos de rotura contraindican el metotrexato y obligan a cirugía.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>ACOG Practice Bulletin 193</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>ACOG Practice Bulletin 193: Tubal Ectopic Pregnancy, Obstet Gynecol 2018 (doi:10.1097/AOG.0000000000002560)</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>El hemoperitoneo por sí solo no es contraindicación absoluta; sí la inestabilidad o la rotura (ACOG PB 193). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -13194,12 +14110,24 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Medscape, manejo del desprendimiento de placenta</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>Towers CV et al., Is tocolysis safe in the management of third-trimester bleeding?, Am J Obstet Gynecol 1999 (doi:10.1016/s0002-9378(99)70053-0); Hladky K et al., Placental Abruption, Obstet Gynecol Surv 2002</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente (Medscape no es fuente primaria). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -13253,9 +14181,21 @@
           <t>OMS, uterotónicos para la prevención de HPP; ficha técnica de ergometrina</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>FIGO 2022 (doi:10.1002/ijgo.14116): oxitocina primera línea; ergot tras excluir hipertensión</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -13309,9 +14249,21 @@
           <t>FIGO 2022, recomendaciones de manejo de la HPP</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>FIGO 2022: definición clásica &gt;500 mL vaginal, &gt;1000 mL cesárea</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -13365,9 +14317,21 @@
           <t>Farmacología de agonistas beta-2 (relajan el útero); la hemorragia materna con inestabilidad contraindica los tocolíticos</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient data: sin fuente específica localizada; el mecanismo (tocolítico) es farmacología básica</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -13421,9 +14385,21 @@
           <t>FIGO, recomendaciones de buena práctica en parto pretérmino; contraindicación absoluta de tocólisis en infección intraamniótica</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Insufficient data: fuente no localizada en PubMed</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -13477,9 +14453,21 @@
           <t>ACOG Practice Bulletin 222: Gestational Hypertension and Preeclampsia (2020)</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>ACOG PB 222 no localizada en PubMed</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -13533,9 +14521,21 @@
           <t>CDC/ACIP, Prevention of Measles, Rubella, CRS, and Mumps (MMWR 2013)</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>ACIP 2013 (PMID 23760231): evitar el embarazo tras vacuna con rubéola</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -13589,9 +14589,21 @@
           <t>OMS/AIEPI, Plan C</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Plan C OMS/AIEPI no indexado</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -13645,9 +14657,21 @@
           <t>OMS/AIEPI, Plan C</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Plan C OMS/AIEPI no indexado</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -13701,9 +14725,21 @@
           <t>AHA/AAP, Neonatal Resuscitation Program, 8a ed. (2021)</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>AHA 2020 (doi:10.1161/CIR.0000000000000902) localizada</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -13757,9 +14793,21 @@
           <t>AHA/AAP, Neonatal Resuscitation Program, 8a ed. (2021)</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>IV 0.01-0.03 mg/kg (Ramsie 2024, doi:10.1159/000535502; ILCOR)</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -13813,9 +14861,21 @@
           <t>AHA/AAP, Neonatal Resuscitation Program, 8a ed. (2021)</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>FC &lt;60 tras 30 s de ventilación (ILCOR; Ramachandran 2022)</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -13869,9 +14929,21 @@
           <t>AAP, Clinical Report: Hypertrophic Pyloric Stenosis; Hernanz-Schulman, Radiology (2003)</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>La fuente citada ('AAP Clinical Report') no se localizó; Insufficient data</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -13925,9 +14997,21 @@
           <t>APA, Practice Guideline for the Assessment and Treatment of Patients with Suicidal Behaviors (2010)</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>APA 2010 no localizada en PubMed</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -13978,12 +15062,24 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>NICE NG225, Self-harm: assessment, management and preventing recurrence (2022)</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>NICE NG225 (2022); Steeg S et al., Accuracy of risk scales for predicting repeat self-harm and suicide, BMC Psychiatry 2018 (doi:10.1186/s12888-018-1693-z): AUC 51% para SAD PERSONS</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente: Steeg 2018 (AUC 51%). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -14037,9 +15133,21 @@
           <t>CANMAT/ISBD, Guidelines for the Management of Patients with Bipolar Disorder (2018)</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>CANMAT/ISBD localizada (doi:10.1111/bdi.13135)</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -14085,17 +15193,29 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Navarro: Tras un síndrome neuroléptico maligno se espera al menos 2 semanas antes de reintroducir un antipsicótico, con una dosis baja y vigilancia estrecha.</t>
+          <t>Navarro: Tras un síndrome neuroléptico maligno el antipsicótico se reintroduce solo después de un periodo sin fármaco (suele recomendarse al menos 2 semanas), de preferencia con otro agente, a dosis baja y con vigilancia estrecha.</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Treatment of Patients with Schizophrenia (2020); Strawn et al., Am J Psychiatry (2007)</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>Pileggi DJ, Cook AM, Neuroleptic Malignant Syndrome, Ann Pharmacother 2016 (doi:10.1177/1060028016657553); Strawn JR et al., Am J Psychiatry 2007 (doi:10.1176/ajp.2007.164.6.870)</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Periodo sin fármaco y cambio de agente (Pileggi 2016); '2 semanas' queda como 'suele recomendarse'. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -14149,9 +15269,21 @@
           <t>APA, Practice Guideline for the Treatment of Patients with Schizophrenia (2020)</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>APA 2020 no localizada en PubMed</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N64"/>
@@ -14257,7 +15389,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dolor y sangrado transvaginal con choque hipovolémico serían el cuadro de un ectópico roto. Aquí la presión es normal y el cuadro orienta a un foco infeccioso intestinal: apendicitis.</t>
+          <t>Dolor y sangrado transvaginal con choque hipovolémico serían el cuadro de un ectópico roto. Aquí la presión es normal, no hay sangrado transvaginal y el cuadro orienta a apendicitis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -14265,8 +15397,16 @@
           <t>Estaba como 'aceptar'; describe un diagnóstico que no corresponde al paciente. Ahora es 'descartar'.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>El comentario ahora menciona que no hay sangrado transvaginal. Pendiente para el revisor: en mujer en edad fértil, ¿añadir prueba de embarazo? (sin fuente verificada). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -14292,7 +15432,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Castillo: La epiglotitis cursa con fiebre alta, babeo, posición de trípode y sin tos perruna. Este paciente tiene tos perruna y mejora con el aire frío: es crup.</t>
+          <t>Castillo: La epiglotitis cursa con fiebre alta, babeo, posición de trípode y sin tos perruna. Este paciente tiene estridor y mejora con el aire frío: el cuadro es de crup.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -14300,8 +15440,16 @@
           <t>Estaba como 'aceptar'; describe un diagnóstico que no corresponde al paciente. Ahora es 'descartar'.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>El escenario de CRUP_001_002 no menciona tos perruna; el comentario ya no la afirma. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
@@ -14335,8 +15483,16 @@
           <t>Estaba como 'aceptar'; describe un diagnóstico que no corresponde al paciente. Ahora es 'descartar'.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>José, 32 años: el comentario corresponde al paciente</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr"/>
     </row>
   </sheetData>
@@ -15176,17 +16332,29 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Navarro: En el infarto con choque cardiogénico la reperfusión de elección es la ICP, sin importar el tiempo de retraso. La fibrinólisis queda como último recurso.</t>
+          <t>Navarro: En el infarto con choque cardiogénico la reperfusión de elección es la ICP inmediata. La fibrinólisis solo se considera si la ICP no puede hacerse a tiempo.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017); ESC Guidelines on ACS (2023)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Samsky MD et al., Cardiogenic Shock After Acute Myocardial Infarction: A Review, JAMA 2021 (doi:10.1001/jama.2021.18323); Thiele H et al., CULPRIT-SHOCK, NEJM 2017 (doi:10.1056/NEJMoa1710261)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Comentario: ICP inmediata; fibrinólisis solo si la ICP no llega a tiempo. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -15240,9 +16408,17 @@
           <t>ESC Guidelines on ACS (2023); ACC/AHA STEMI (2013)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -15296,9 +16472,17 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -15500,17 +16684,29 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Mendoza: La meta es una ICP primaria en 90 minutos o menos desde el primer contacto médico; si no se logra, se considera fibrinólisis.</t>
+          <t>Mendoza: La ICP primaria se hace lo antes posible; si no puede realizarse dentro de los 120 minutos siguientes al diagnóstico, se administra fibrinólisis.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>Bhatt DL et al., Diagnosis and Treatment of Acute Coronary Syndromes: A Review, JAMA 2022 (doi:10.1001/jama.2022.0358); Vogel B et al., Nat Rev Dis Primers 2019 (doi:10.1038/s41572-019-0090-3)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Comentario: umbral de 120 min desde el diagnóstico, no 90 min desde el primer contacto. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N8"/>
@@ -16091,9 +17287,21 @@
           <t>ATLS 10a ed., Capítulo 3 (Choque) y Capítulo 4 (Trauma torácico)</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. es un libro, no indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -16147,9 +17355,21 @@
           <t>ATLS 10a ed., Capítulo 3 (Choque obstructivo) y Capítulo 4</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. es un libro, no indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -16255,9 +17475,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis (J Hepatobiliary Pancreat Sci 2018)</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>TG18 (doi:10.1002/jhbp.509): drenaje biliar en colangitis moderada/grave</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -16311,9 +17543,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>TG18: tratamiento inmediato sin esperar diagnóstico definitivo; SSC 2021: antimicrobiano en 1 h</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -16367,9 +17611,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>TG18 (doi:10.1002/jhbp.509)</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -16475,9 +17731,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis (J Hepatobiliary Pancreat Sci 2018)</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>TG18 (doi:10.1002/jhbp.509): drenaje biliar en colangitis moderada/grave</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -16531,9 +17799,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>TG18: tratamiento inmediato sin esperar diagnóstico definitivo; SSC 2021: antimicrobiano en 1 h</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -16587,9 +17867,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>TG18 (doi:10.1002/jhbp.509)</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -16796,12 +18088,24 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>WSES, Management of Adhesive Small Bowel Obstruction Guidelines (2017)</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>Ponte CD, Nappi JM, Review of a new gastrointestinal drug: metoclopramide, Am J Hosp Pharm 1981 (doi:10.1093/ajhp/38.6.829): contraindicada en obstrucción, hemorragia o perforación gastrointestinal; ficha técnica</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Solo la fuente (la citada no trata metoclopramida). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -16907,9 +18211,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulo 3</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. no indexado</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -16963,9 +18279,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulos 3 y 4</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. no indexado</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -17123,9 +18451,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulo 3</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. no indexado</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -17179,9 +18519,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulos 3 y 4</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. es un libro, no indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -17235,9 +18587,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulos 3 y 4</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>ATLS 10a ed. es un libro, no indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -17721,9 +19085,21 @@
           <t>ADA, Hyperglycemic Crises in Adults with Diabetes: A Consensus Report (2024)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ADA 2024 (doi:10.2337/dci24-0032) localizada; texto confirmado en JBDS: insulina fija hasta resolver la cetosis y glucosa al bajar</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -18044,9 +19420,21 @@
           <t>ASCRS, Clinical Practice Guidelines for Left-Sided Colonic Diverticulitis (2020)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ASCRS 2020 (doi:10.1097/DCR.0000000000001679) sin resumen</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -18204,9 +19592,21 @@
           <t>ESVS, Guidelines on the Management of Diseases of Mesenteric Arteries (2017); WSES (2022)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2022 (doi:10.1186/s13017-022-00443-x): heparina temprana mejora la supervivencia</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -18260,9 +19660,21 @@
           <t>WSES, Acute Mesenteric Ischemia Guidelines (2022)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2022: vasopresores con cautela; eliminarlos es medida primaria</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -18316,9 +19728,21 @@
           <t>WSES, Acute Mesenteric Ischemia Guidelines (2022)</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2022</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -18416,17 +19840,29 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Navarro: La estrategia es restrictiva, con umbral de 7 g/dL y meta de 7 a 9. Sobretransfundir eleva la presión portal y favorece el resangrado.</t>
+          <t>Navarro: La estrategia es restrictiva: se transfunde con hemoglobina cercana a 7 g/dL y la meta es de 7 a 8 g/dL. Sobretransfundir eleva la presión portal y favorece el resangrado.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Baveno VII Consensus (J Hepatol 2022); AASLD Guidance on Portal Hypertensive Bleeding (2017)</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>Baveno VII, J Hepatol 2022 (doi:10.1016/j.jhep.2021.12.022), recomendación 6.2; Villanueva C et al., NEJM 2013 (doi:10.1056/NEJMoa1211801)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Meta 7-8 g/dL (Baveno VII 6.2), no 7-9. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -18532,9 +19968,21 @@
           <t>Baveno VII Consensus (J Hepatol 2022)</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Baveno VII 7.7: reducir o suspender BBNS con PAS &lt;90 o PAM &lt;65</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N12"/>

--- a/REVISION_CLINICA/revision_clinica.xlsx
+++ b/REVISION_CLINICA/revision_clinica.xlsx
@@ -5775,22 +5775,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Farmacología de agonistas beta-2 (relajan el útero); la hemorragia materna con inestabilidad contraindica los tocolíticos</t>
+          <t>Lee HL et al., Medicine 2020 (doi:10.1097/md.0000000000023651): los tocolíticos aumentan la hemorragia por atonía (betamiméticos aHR 1.71); FIGO 2022: oxitocina de primera línea</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Insufficient data: sin fuente específica localizada; el mecanismo (tocolítico) es farmacología básica</t>
+          <t>Solo la fuente: Lee 2020 (tocolíticos y hemorragia por atonía). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5947,22 +5947,22 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>FIGO, recomendaciones de buena práctica en parto pretérmino; contraindicación absoluta de tocólisis en infección intraamniótica</t>
+          <t>CNGOF, Schmitz T et al., Eur J Obstet Gynecol Reprod Biol 2019 (doi:10.1016/j.ejogrb.2019.02.021): ante infección intrauterina, antibiótico IV inmediato y nacimiento temprano (grado A); ACOG Committee Opinion 712 (2017)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Insufficient data: fuente no localizada en PubMed</t>
+          <t>Solo la fuente: CNGOF 2019 (infección intrauterina: nacimiento temprano, grado A). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6223,22 +6223,22 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>ACOG Practice Bulletin 222: Gestational Hypertension and Preeclampsia (2020)</t>
+          <t>Duley L et al., Magnesium sulphate versus diazepam for eclampsia, Cochrane 2010 (doi:10.1002/14651858.CD000127.pub2): menos muertes maternas (RR 0.59) y menos convulsiones recurrentes (RR 0.43); ACOG PB 222 (2020)</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>ACOG PB 222 no localizada en PubMed</t>
+          <t>Solo la fuente: Cochrane, Duley 2010. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8200,22 +8200,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>OMS/AIEPI, Plan C</t>
+          <t>OMS, Plan C; Houston KA et al., GASTRO, BMC Med 2019 (doi:10.1186/s12916-019-1356-z): Plan C = rehidratación IV con bolos para el choque; Maitland K et al., NEJM 2025 (doi:10.1056/NEJMoa2505752): bolos IV para el choque incluso en el brazo oral</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Plan C OMS/AIEPI no indexado</t>
+          <t>Solo la fuente: Houston 2019 y Maitland 2025 (choque = bolos IV). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8528,22 +8528,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>OMS/AIEPI, Plan C</t>
+          <t>OMS, Plan C; Houston KA et al., GASTRO, BMC Med 2019 (doi:10.1186/s12916-019-1356-z): Plan C = rehidratación IV con bolos para el choque; Maitland K et al., NEJM 2025 (doi:10.1056/NEJMoa2505752): bolos IV para el choque incluso en el brazo oral</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Plan C OMS/AIEPI no indexado</t>
+          <t>Solo la fuente: Houston 2019 y Maitland 2025 (choque = bolos IV). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9372,22 +9372,22 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>AAP, Clinical Report: Hypertrophic Pyloric Stenosis; Hernanz-Schulman, Radiology (2003)</t>
+          <t>Gilbertson LE et al., Anesth Analg 2019 (doi:10.1213/ane.0000000000004446): la alcalosis es una urgencia médica y se asocia a apnea; Spicer RD, Br J Surg 1982 (doi:10.1002/bjs.1800690304): corrección hidroelectrolítica preoperatoria esencial</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>La fuente citada ('AAP Clinical Report') no se localizó; Insufficient data</t>
+          <t>La fuente citada ('AAP Clinical Report') no existe en PubMed; sustituida por Gilbertson 2019 y Spicer 1982. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10383,22 +10383,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Assessment and Treatment of Patients with Suicidal Behaviors (2010)</t>
+          <t>Mann JJ et al., JAMA 2005 (doi:10.1001/jama.294.16.2064) y Zalsman G et al., Lancet Psychiatry 2016 (doi:10.1016/s2215-0366(16)30030-x): restringir el acceso a medios letales, incluidos fármacos, previene el suicidio</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>APA 2010 no localizada en PubMed</t>
+          <t>Solo la fuente: Mann 2005, Zalsman 2016 (restricción de medios letales). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -10910,27 +10910,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Navarro: La clozapina exige vigilar el recuento de neutrófilos de forma periódica, porque puede causar agranulocitosis grave.</t>
+          <t>Navarro: La clozapina exige vigilar el recuento de neutrófilos de forma periódica, sobre todo en los primeros 2 años, porque puede causar agranulocitosis grave.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Treatment of Patients with Schizophrenia (2020)</t>
+          <t>Siskind D et al., consenso Delphi global, Lancet Psychiatry 2025 (doi:10.1016/s2215-0366(25)00098-7): vigilancia de neutrófilos durante los primeros 2 años; Zhou H et al., Br J Psychiatry 2026: riesgo máximo en las primeras 18 semanas</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>APA 2020 no localizada en PubMed</t>
+          <t>Comentario: precisa los primeros 2 años (Siskind 2025, consenso Delphi global). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14314,22 +14314,22 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Farmacología de agonistas beta-2 (relajan el útero); la hemorragia materna con inestabilidad contraindica los tocolíticos</t>
+          <t>Lee HL et al., Medicine 2020 (doi:10.1097/md.0000000000023651): los tocolíticos aumentan la hemorragia por atonía (betamiméticos aHR 1.71); FIGO 2022: oxitocina de primera línea</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Insufficient data: sin fuente específica localizada; el mecanismo (tocolítico) es farmacología básica</t>
+          <t>Solo la fuente: Lee 2020 (tocolíticos y hemorragia por atonía). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14382,22 +14382,22 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>FIGO, recomendaciones de buena práctica en parto pretérmino; contraindicación absoluta de tocólisis en infección intraamniótica</t>
+          <t>CNGOF, Schmitz T et al., Eur J Obstet Gynecol Reprod Biol 2019 (doi:10.1016/j.ejogrb.2019.02.021): ante infección intrauterina, antibiótico IV inmediato y nacimiento temprano (grado A); ACOG Committee Opinion 712 (2017)</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Insufficient data: fuente no localizada en PubMed</t>
+          <t>Solo la fuente: CNGOF 2019 (infección intrauterina: nacimiento temprano, grado A). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14450,22 +14450,22 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>ACOG Practice Bulletin 222: Gestational Hypertension and Preeclampsia (2020)</t>
+          <t>Duley L et al., Magnesium sulphate versus diazepam for eclampsia, Cochrane 2010 (doi:10.1002/14651858.CD000127.pub2): menos muertes maternas (RR 0.59) y menos convulsiones recurrentes (RR 0.43); ACOG PB 222 (2020)</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>ACOG PB 222 no localizada en PubMed</t>
+          <t>Solo la fuente: Cochrane, Duley 2010. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14586,22 +14586,22 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>OMS/AIEPI, Plan C</t>
+          <t>OMS, Plan C; Houston KA et al., GASTRO, BMC Med 2019 (doi:10.1186/s12916-019-1356-z): Plan C = rehidratación IV con bolos para el choque; Maitland K et al., NEJM 2025 (doi:10.1056/NEJMoa2505752): bolos IV para el choque incluso en el brazo oral</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Plan C OMS/AIEPI no indexado</t>
+          <t>Solo la fuente: Houston 2019 y Maitland 2025 (choque = bolos IV). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14654,22 +14654,22 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>OMS/AIEPI, Plan C</t>
+          <t>OMS, Plan C; Houston KA et al., GASTRO, BMC Med 2019 (doi:10.1186/s12916-019-1356-z): Plan C = rehidratación IV con bolos para el choque; Maitland K et al., NEJM 2025 (doi:10.1056/NEJMoa2505752): bolos IV para el choque incluso en el brazo oral</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Plan C OMS/AIEPI no indexado</t>
+          <t>Solo la fuente: Houston 2019 y Maitland 2025 (choque = bolos IV). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14926,22 +14926,22 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>AAP, Clinical Report: Hypertrophic Pyloric Stenosis; Hernanz-Schulman, Radiology (2003)</t>
+          <t>Gilbertson LE et al., Anesth Analg 2019 (doi:10.1213/ane.0000000000004446): la alcalosis es una urgencia médica y se asocia a apnea; Spicer RD, Br J Surg 1982 (doi:10.1002/bjs.1800690304): corrección hidroelectrolítica preoperatoria esencial</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>La fuente citada ('AAP Clinical Report') no se localizó; Insufficient data</t>
+          <t>La fuente citada ('AAP Clinical Report') no existe en PubMed; sustituida por Gilbertson 2019 y Spicer 1982. Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14994,22 +14994,22 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Assessment and Treatment of Patients with Suicidal Behaviors (2010)</t>
+          <t>Mann JJ et al., JAMA 2005 (doi:10.1001/jama.294.16.2064) y Zalsman G et al., Lancet Psychiatry 2016 (doi:10.1016/s2215-0366(16)30030-x): restringir el acceso a medios letales, incluidos fármacos, previene el suicidio</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>APA 2010 no localizada en PubMed</t>
+          <t>Solo la fuente: Mann 2005, Zalsman 2016 (restricción de medios letales). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15261,27 +15261,27 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Navarro: La clozapina exige vigilar el recuento de neutrófilos de forma periódica, porque puede causar agranulocitosis grave.</t>
+          <t>Navarro: La clozapina exige vigilar el recuento de neutrófilos de forma periódica, sobre todo en los primeros 2 años, porque puede causar agranulocitosis grave.</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Treatment of Patients with Schizophrenia (2020)</t>
+          <t>Siskind D et al., consenso Delphi global, Lancet Psychiatry 2025 (doi:10.1016/s2215-0366(25)00098-7): vigilancia de neutrófilos durante los primeros 2 años; Zhou H et al., Br J Psychiatry 2026: riesgo máximo en las primeras 18 semanas</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Aprobar</t>
+          <t>Corregir</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>APA 2020 no localizada en PubMed</t>
+          <t>Comentario: precisa los primeros 2 años (Siskind 2025, consenso Delphi global). Aplicada el 2026-10-13 (tools/apply_clinical_review_2026_10.py)</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/REVISION_CLINICA/revision_clinica.xlsx
+++ b/REVISION_CLINICA/revision_clinica.xlsx
@@ -724,12 +724,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>DHHS, Guidelines for the Use of Antiretroviral Agents in Adults and Adolescents with HIV</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Saag 2018 (doi:10.1001/jama.2018.8431): TAR lo antes posible; el genotipo se solicita pero no se espera</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Saag 2018 (doi:10.1001/jama.2018.8431): TAR lo antes posible; el genotipo se solicita pero no se espera</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -776,12 +788,24 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>DHHS, Guidelines for the Use of Antiretroviral Agents in Adults and Adolescents with HIV</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Coffey 2019 (doi:10.1097/qad.0000000000002124): inicio inmediato con 51 % de consumo de sustancias y 92 % de supresión viral</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Coffey 2019 (doi:10.1097/qad.0000000000002124): inicio inmediato con 51 % de consumo de sustancias y 92 % de supresión viral</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -899,9 +923,21 @@
           <t>IDSA, Practice Guidelines for Bacterial Meningitis (Tunkel et al., Clin Infect Dis 2004)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>IDSA 2004 (doi:10.1086/425368) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -948,12 +984,24 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>IDSA, Practice Guidelines for Bacterial Meningitis (Tunkel et al., Clin Infect Dis 2004)</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>de Gans 2002 (doi:10.1056/nejmoa021334): dexametasona 15-20 min antes o junto con la primera dosis de antibiótico</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>de Gans 2002 (doi:10.1056/nejmoa021334): dexametasona 15-20 min antes o junto con la primera dosis de antibiótico</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1000,12 +1048,24 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Surviving Sepsis Campaign 2021</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>Surviving Sepsis 2021 (doi:10.1007/s00134-021-06506-y): norepinefrina de primera línea, no almidones, PAM de 65</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Surviving Sepsis 2021 (doi:10.1007/s00134-021-06506-y): norepinefrina de primera línea, no almidones, PAM de 65</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1120,12 +1180,24 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Surviving Sepsis Campaign 2021</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>Surviving Sepsis 2021 (doi:10.1007/s00134-021-06506-y): norepinefrina de primera línea, no almidones, PAM de 65</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Surviving Sepsis 2021 (doi:10.1007/s00134-021-06506-y): norepinefrina de primera línea, no almidones, PAM de 65</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1172,12 +1244,24 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Surviving Sepsis Campaign 2021</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>Surviving Sepsis 2021 (doi:10.1007/s00134-021-06506-y): norepinefrina de primera línea, no almidones, PAM de 65</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Surviving Sepsis 2021 (doi:10.1007/s00134-021-06506-y): norepinefrina de primera línea, no almidones, PAM de 65</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1292,12 +1376,24 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>CDC, guías de tratamiento de ITS 2021</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>CDC ITS 2021: las pruebas treponémicas suelen quedar reactivas de por vida</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>CDC ITS 2021: las pruebas treponémicas suelen quedar reactivas de por vida</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1344,12 +1440,24 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>CDC, guías de tratamiento de ITS 2021</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>CDC ITS 2021: respuesta = caída de cuatro veces en 12 meses</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>CDC ITS 2021: respuesta = caída de cuatro veces en 12 meses</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1396,12 +1504,24 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>CDC, guías de tratamiento de ITS 2021</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>CDC ITS 2021: ceftriaxona 500 mg IM para gonorrea; penicilina G benzatínica 2.4 MU para sífilis</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>CDC ITS 2021: ceftriaxona 500 mg IM para gonorrea; penicilina G benzatínica 2.4 MU para sífilis</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N14"/>
@@ -1562,9 +1682,21 @@
           <t>Falso amigo clásico inglés-español</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Vocabulario médico inglés-español de diccionario</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1614,9 +1746,21 @@
           <t>Falso amigo clásico inglés-español</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Vocabulario médico inglés-español de diccionario</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1666,9 +1810,21 @@
           <t>Vocabulario médico inglés-español</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Vocabulario médico inglés-español de diccionario</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1718,9 +1874,21 @@
           <t>Falso amigo clásico inglés-español</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Vocabulario médico inglés-español de diccionario</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1770,9 +1938,21 @@
           <t>Falso amigo clásico inglés-español; terminología de exploración física</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Vocabulario médico inglés-español de diccionario</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N6"/>
@@ -2190,12 +2370,24 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>GINA 2024</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>EAACI 2025 (doi:10.1111/all.70091) y Ramakrishnan 2021: los antibióticos no se recomiendan de rutina en la exacerbación</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>EAACI 2025 (doi:10.1111/all.70091) y Ramakrishnan 2021: los antibióticos no se recomiendan de rutina en la exacerbación</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -2245,9 +2437,21 @@
           <t>GINA 2024</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>GINA localizada; sin texto</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -2361,9 +2565,21 @@
           <t>ADA, Standards of Care: clasificación y diagnóstico</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>ADA Standards of Care 2024 (doi:10.2337/dc24-s002) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -2413,9 +2629,21 @@
           <t>ADA, Standards of Care: clasificación y diagnóstico</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>ADA Standards of Care 2024 (doi:10.2337/dc24-s002) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2465,9 +2693,21 @@
           <t>ADA, Standards of Care (criterios diagnósticos)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>ADA Standards of Care 2024 (doi:10.2337/dc24-s002) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -2517,9 +2757,21 @@
           <t>ADA, Standards of Care: tratamiento farmacológico</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>ADA Standards of Care 2024 (doi:10.2337/dc24-s002) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2566,12 +2818,24 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>ESC 2021, guía de insuficiencia cardiaca</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>Nesti 2021 (doi:10.1186/s12933-021-01294-7): la pioglitazona aumenta la hospitalización por IC por retención de líquidos; ESC 2021 localizada</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Nesti 2021 (doi:10.1186/s12933-021-01294-7): la pioglitazona aumenta la hospitalización por IC por retención de líquidos; ESC 2021 localizada</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -2618,12 +2882,24 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>AHA/ACC/HFSA 2022; AHA, fármacos que causan o agravan la IC</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>Holt 2023 (doi:10.1016/j.jacc.2023.02.027): los AINE se asocian a hospitalización por IC (OR 1.43)</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Holt 2023 (doi:10.1016/j.jacc.2023.02.027): los AINE se asocian a hospitalización por IC (OR 1.43)</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -2673,9 +2949,21 @@
           <t>Digitalis Investigation Group, NEJM 1997</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>DIG original: sin efecto en mortalidad; análisis post hoc (Ahmed 2005, doi:10.1093/eurheartj/ehi687) matiza según concentración</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2725,9 +3013,21 @@
           <t>ESC 2021, guía de insuficiencia cardiaca</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>ESC 2021 (doi:10.1093/eurheartj/ehab368) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2774,12 +3074,24 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>ACC/AHA, Guideline for High Blood Pressure in Adults (2017); ESC/ESH Guidelines (2018)</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>Makani 2013 (doi:10.1136/bmj.f360): el doble bloqueo no reduce la mortalidad y aumenta hiperpotasemia, hipotensión e insuficiencia renal</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Makani 2013 (doi:10.1136/bmj.f360): el doble bloqueo no reduce la mortalidad y aumenta hiperpotasemia, hipotensión e insuficiencia renal</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -3146,12 +3458,24 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>ESC 2019, guía de embolia pulmonar</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>ACEP 2018 (doi:10.1016/j.annemergmed.2018.03.006): el dímero D se aplica a probabilidad baja o intermedia</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>ACEP 2018 (doi:10.1016/j.annemergmed.2018.03.006): el dímero D se aplica a probabilidad baja o intermedia</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -3201,9 +3525,21 @@
           <t>ESC 2019, guía de embolia pulmonar</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Duffett, BMJ 2020 (doi:10.1136/bmj.m2177) y ESC 2019 localizadas, sin texto para esta afirmación</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -3253,9 +3589,21 @@
           <t>ESC 2019, guía de embolia pulmonar</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Duffett, BMJ 2020 (doi:10.1136/bmj.m2177) y ESC 2019 localizadas, sin texto para esta afirmación</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N25"/>
@@ -3416,9 +3764,21 @@
           <t>Niveles de prevención de Leavell y Clark</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Niveles de prevención de Leavell y Clark; definición de texto</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -3468,9 +3828,21 @@
           <t>Niveles de prevención de Leavell y Clark</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Niveles de prevención de Leavell y Clark; definición de texto</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -3520,9 +3892,21 @@
           <t>Prevención cuaternaria (Jamoulle); carta de prevención cuaternaria del mismo mazo</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Niveles de prevención de Leavell y Clark; definición de texto</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -3572,9 +3956,21 @@
           <t>Historia natural de la enfermedad (Leavell y Clark)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Niveles de prevención de Leavell y Clark; definición de texto</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -3624,9 +4020,21 @@
           <t>Leavell HR, Clark EG, Preventive Medicine for the Doctor in His Community (1965)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Niveles de prevención de Leavell y Clark; definición de texto</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -3676,9 +4084,21 @@
           <t>Leavell HR, Clark EG, Preventive Medicine for the Doctor in His Community (1965)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Niveles de prevención de Leavell y Clark; definición de texto</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -3864,9 +4284,21 @@
           <t>OMS, Rabies Vaccines: Position Paper (2018)</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>ACIP 2008 (PMID 18496505) localizada; el resumen no detalla la infiltración</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N10"/>
@@ -4024,12 +4456,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>AHA/ASA, Guidelines for the Management of Aneurysmal SAH (2012); ACEP Clinical Policy: Acute Headache (2019)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Perry 2019 (doi:10.1161/strokeaha.119.026969): TC primero; punción lumbar si la TC es negativa y pasaron más de 6 h</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Perry 2019 (doi:10.1161/strokeaha.119.026969): TC primero; punción lumbar si la TC es negativa y pasaron más de 6 h</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -4076,12 +4520,24 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>ACEP Clinical Policy: Acute Headache (2019); AHA/ASA, Guidelines for the Management of Aneurysmal SAH (2012)</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Aaseth 2024 (doi:10.1111/ene.16385) y Perry 2019: una TC normal dentro de 6 h descarta HSA; después, no</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Aaseth 2024 (doi:10.1111/ene.16385) y Perry 2019: una TC normal dentro de 6 h descarta HSA; después, no</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -4191,17 +4647,29 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Mendoza: Para trombolizar basta con TA menor de 185/110 y mantenerla menor de 180/105 en las siguientes 24 horas; bajarla de más reduce la perfusión de la penumbra.</t>
+          <t>Mendoza: Para trombolizar basta con TA menor de 185/110 y mantenerla menor de 180/105 durante las siguientes 24 horas. Bajarla más de lo necesario no mejora el desenlace y retrasa el tratamiento.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>AHA/ASA 2019, manejo temprano del EVC isquémico</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>ESO 2026 (doi:10.1093/esj/aakag004) &lt;185/110 antes y &lt;180/105 durante 24 h; ENCHANTED (doi:10.1016/s0140-6736(19)30038-8): bajar más no mejora el desenlace</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Solo el comentario: ESO 2026 (doi:10.1093/esj/aakag004) &lt;185/110 antes y &lt;180/105 durante 24 h; ENCHANTED (doi:10.1016/s0140-6736(19)30038-8): bajar más no mejora el desenlace Aplicada el 2026-10-13.</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -4319,9 +4787,21 @@
           <t>AHA/ASA 2019, manejo temprano del EVC isquémico</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>AHA/ASA 2019 (doi:10.1161/STR.0000000000000211) y ESO 2021 (doi:10.1177/2396987321989865) localizadas, sin texto para esta afirmación</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -4371,9 +4851,21 @@
           <t>AHA/ASA 2019, manejo temprano del EVC isquémico</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>AHA/ASA 2019 (doi:10.1161/STR.0000000000000211) y ESO 2021 (doi:10.1177/2396987321989865) localizadas, sin texto para esta afirmación</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N8"/>
@@ -4531,12 +5023,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ACOG Practice Bulletin 190: Gestational Diabetes Mellitus (2018)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Balsells, BMJ 2015 (doi:10.1136/bmj.h102) y Sénat, JAMA 2018 (doi:10.1001/jama.2018.4072): la glibenclamida no debe ser primera línea</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Balsells, BMJ 2015 (doi:10.1136/bmj.h102) y Sénat, JAMA 2018 (doi:10.1001/jama.2018.4072): la glibenclamida no debe ser primera línea</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -4586,9 +5090,21 @@
           <t>ACOG Practice Bulletin 190: Gestational Diabetes Mellitus (2018)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ACOG localizada sin texto; práctica obstétrica estándar</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -4638,9 +5154,21 @@
           <t>ADA, Standards of Care in Diabetes: Management of Diabetes in Pregnancy</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>ACOG localizada sin texto; práctica obstétrica estándar</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -4690,9 +5218,21 @@
           <t>OMS, Safe abortion: technical and policy guidance (2012); ACOG Practice Bulletin 200 (2018)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>ACOG localizada sin texto; práctica obstétrica estándar</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -4878,9 +5418,21 @@
           <t>AJOG, desprendimiento de placenta a término y cerca del término; Medscape</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>ACOG localizada sin texto; práctica obstétrica estándar</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -4930,9 +5482,21 @@
           <t>ACOG Practice Bulletin 193</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>ACOG PB 193 (doi:10.1097/AOG.0000000000002560) localizada; sin texto sobre ácido fólico</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -4982,9 +5546,21 @@
           <t>ACOG Practice Bulletin 193</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>ACOG PB 193 localizada; sin texto sobre AINE</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -5031,12 +5607,24 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>ACOG Practice Bulletin 193</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>Kirk 2007 (doi:10.1093/humrep/del433): descenso &gt;15 % entre los días 4 y 7 predice éxito</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Kirk 2007 (doi:10.1093/humrep/del433): descenso &gt;15 % entre los días 4 y 7 predice éxito</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -5154,9 +5742,21 @@
           <t>ACOG Practice Bulletin 193</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Alur-Gupta 2019 (doi:10.1097/ogx.0000000000000750): hCG alta se asocia a menor éxito con dosis única</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -5198,17 +5798,29 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Castillo: El DIU se difiere al menos 6 semanas tras la evacuación y hasta que la hCG sea normal, por riesgo de perforación uterina; en el seguimiento se usan anticonceptivos orales.</t>
+          <t>Castillo: El DIU suele diferirse hasta que la hCG sea normal por el riesgo de perforación y sangrado; las guías no coinciden y la evidencia no muestra más neoplasia con él. En el seguimiento se prefieren métodos hormonales o de barrera.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Ngan et al., FIGO 2018, enfermedad trofoblástica gestacional</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>hay desacuerdo entre guías (RCOG 2010 vs OMS/CDC); la evidencia (Gaffield 2009, doi:10.1016/j.contraception.2009.03.022; Hagey 2024, doi:10.1016/j.contraception.2024.110488) no muestra más neoplasia con DIU. Se sugiere confirmación médica</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Solo el comentario: hay desacuerdo entre guías (RCOG 2010 vs OMS/CDC); la evidencia (Gaffield 2009, doi:10.1016/j.contraception.2009.03.022; Hagey 2024, doi:10.1016/j.contraception.2024.110488) no muestra más neoplasia con DIU. Se sugiere confirmación médica Aplicada el 2026-10-13.</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -5250,17 +5862,29 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Castillo: La quimioprofilaxis se limita a situaciones de riesgo alto o cuando el seguimiento con hCG no es posible; no es de rutina.</t>
+          <t>Castillo: La quimioprofilaxis no es de rutina: la evidencia es de baja calidad y puede retrasar el diagnóstico del tumor y aumentar la resistencia a la quimioterapia. Solo se discute en la mola completa de alto riesgo.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Ngan et al., FIGO 2018, enfermedad trofoblástica gestacional</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>Cochrane 2017 (doi:10.1002/14651858.cd007289.pub3): la quimioprofilaxis no puede recomendarse por la baja calidad de la evidencia</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Solo el comentario: Cochrane 2017 (doi:10.1002/14651858.cd007289.pub3): la quimioprofilaxis no puede recomendarse por la baja calidad de la evidencia Aplicada el 2026-10-13.</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -5310,9 +5934,21 @@
           <t>Ngan et al., FIGO 2018; ACOG, enfermedad trofoblástica gestacional</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Soper 2021 (doi:10.1097/aog.0000000000004240) localizada, sin texto para esta afirmación</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -5362,9 +5998,21 @@
           <t>Medscape, tratamiento de la mola hidatiforme; FIGO 2018</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Soper 2021 (doi:10.1097/aog.0000000000004240) localizada, sin texto para esta afirmación</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -5482,9 +6130,21 @@
           <t>AJOG, desprendimiento de placenta a término y cerca del término; Medscape</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>ACOG localizada sin texto; práctica obstétrica estándar</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -5599,12 +6259,24 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>OMS 2017, recomendación sobre ácido tranexámico; ensayo WOMAN</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>FIGO 2022 (doi:10.1002/ijgo.14116): ácido tranexámico en las primeras 3 h; la histerectomía es la última opción quirúrgica</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>FIGO 2022 (doi:10.1002/ijgo.14116): ácido tranexámico en las primeras 3 h; la histerectomía es la última opción quirúrgica</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -5719,12 +6391,24 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>FIGO 2022 (manejo escalonado)</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>FIGO 2022 (doi:10.1002/ijgo.14116): ácido tranexámico en las primeras 3 h; la histerectomía es la última opción quirúrgica</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>FIGO 2022 (doi:10.1002/ijgo.14116): ácido tranexámico en las primeras 3 h; la histerectomía es la última opción quirúrgica</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -5842,9 +6526,21 @@
           <t>Regla de las 4 T (Medscape, Cleveland Clinic): con útero firme y sangrado persistente se busca trauma, tejido o coagulopatía</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>FIGO 2022 localizada; las 4 T son un recurso mnemotécnico estándar</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -5891,12 +6587,24 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>ACOG Committee Opinion 712 (2017, reafirmada 2022)</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -6011,12 +6719,24 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>ACOG Committee Opinion 712</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -6063,12 +6783,24 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>ACOG Committee Opinion 712; Merck Manual, esquemas para infección intraamniótica</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -6115,12 +6847,24 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>ACOG Committee Opinion 712 (infección sospechada vs. confirmada)</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -6167,12 +6911,24 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>ACOG Committee Opinion 712 (el diagnóstico exige antibióticos y acelerar el nacimiento)</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Conde-Agudelo 2020 (doi:10.1016/j.ajog.2020.09.044) y Jung 2023 (doi:10.1016/j.ajog.2023.02.002): ampicilina más gentamicina, antibiótico intraparto, cesárea solo por indicación obstétrica</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -6282,17 +7038,29 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Castillo: El riesgo de eclampsia persiste en el posparto. El sulfato de magnesio se continúa por 24 horas después del nacimiento.</t>
+          <t>Castillo: El riesgo de eclampsia persiste en el posparto, por eso el esquema estándar mantiene el sulfato de magnesio 24 horas después del nacimiento. Algunos ensayos sugieren que periodos más cortos podrían bastar, pero no es la conducta estándar.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>ACOG Practice Bulletin 222: Gestational Hypertension and Preeclampsia (2020)</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>24 h es el esquema estándar; Vigil-De Gracia 2018 (doi:10.1111/1471-0528.15320) y Okonkwo 2022 (doi:10.1097/aog.0000000000004720) sugieren que periodos más cortos podrían bastar. Se sugiere confirmación médica</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Solo el comentario: 24 h es el esquema estándar; Vigil-De Gracia 2018 (doi:10.1111/1471-0528.15320) y Okonkwo 2022 (doi:10.1097/aog.0000000000004720) sugieren que periodos más cortos podrían bastar. Se sugiere confirmación médica Aplicada el 2026-10-13.</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -6342,9 +7110,21 @@
           <t>ACOG Practice Bulletin 222: Gestational Hypertension and Preeclampsia (2020)</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Contraindicación de IECA en el embarazo: práctica estándar; ACOG localizada</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -6394,9 +7174,21 @@
           <t>Merck Manual; AAFP, RPM pretérmino</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>SOGC 430 (doi:10.1016/j.jogc.2022.08.014) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -6446,9 +7238,21 @@
           <t>AAFP, RPM pretérmino</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>SOGC 430 (doi:10.1016/j.jogc.2022.08.014) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -6495,12 +7299,24 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>ACOG; ensayo de Mercer, esquema de latencia</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>Navathe 2019 (doi:10.1016/j.ajog.2019.03.009) y CNGOF 2019 (doi:10.1016/j.ejogrb.2019.02.021): ampicilina más macrólido 48 h y luego vía oral hasta 7 días</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Navathe 2019 (doi:10.1016/j.ajog.2019.03.009) y CNGOF 2019 (doi:10.1016/j.ejogrb.2019.02.021): ampicilina más macrólido 48 h y luego vía oral hasta 7 días</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N37"/>
@@ -6661,9 +7477,21 @@
           <t>AAO, Preferred Practice Pattern: Primary Angle-Closure Disease (2020)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Práctica estándar; AAO localizada</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -6710,12 +7538,24 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>AAO, Preferred Practice Pattern: Primary Angle-Closure Disease (2020)</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Lam 2002 (doi:10.1016/s0161-6420(02)01158-2): tratamiento médico para bajar la presión mientras se prepara la iridotomía</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Lam 2002 (doi:10.1016/s0161-6420(02)01158-2): tratamiento médico para bajar la presión mientras se prepara la iridotomía</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -6765,9 +7605,21 @@
           <t>AAO, Preferred Practice Pattern: Primary Angle-Closure Disease (2020)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Lam 2002: la pilocarpina forma parte del tratamiento inicial; su ineficacia con presión muy alta es enseñanza estándar</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N4"/>
@@ -6928,9 +7780,21 @@
           <t>AAO-HNS 2020, guía de epistaxis (compresión con el paciente inclinado hacia adelante)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>AAO-HNSF 2020 (doi:10.1177/0194599819890327): compresión firme en el tercio inferior de la nariz; la guía no detalla la posición de la cabeza</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -6977,12 +7841,24 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Merck Manual, cauterio en epistaxis anterior; AAO-HNS 2020</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>AAO-HNSF 2020: el cauterio se limita al sitio o sitios de sangrado</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>AAO-HNSF 2020: el cauterio se limita al sitio o sitios de sangrado</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -7032,9 +7908,21 @@
           <t>Medscape, resumen de guías de epistaxis; AAO-HNS 2020</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>AAO-HNSF 2020: la guía pide documentar factores de sangrado; no menciona estudios de coagulación de rutina</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -7081,12 +7969,24 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>AAO-HNS 2020, guía de epistaxis</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>AAO-HNSF 2020: sin sangrado que ponga en riesgo la vida, los tratamientos de primera línea van antes de revertir o suspender el anticoagulante</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>AAO-HNSF 2020: sin sangrado que ponga en riesgo la vida, los tratamientos de primera línea van antes de revertir o suspender el anticoagulante</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -7133,12 +8033,24 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>AAP 2013, guía de otitis media aguda</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>Frost 2022 (doi:10.1016/j.jpeds.2022.07.053): menos fracasos con amoxicilina que con azitromicina</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Frost 2022 (doi:10.1016/j.jpeds.2022.07.053): menos fracasos con amoxicilina que con azitromicina</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -7185,12 +8097,24 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>AAP 2013, guía de otitis media aguda</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>Marchisio 2019 (doi:10.1097/inf.0000000000002452): antibiótico inmediato en menores de 6 meses</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Marchisio 2019 (doi:10.1097/inf.0000000000002452): antibiótico inmediato en menores de 6 meses</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -7237,12 +8161,24 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>AAP 2013, guía de otitis media aguda</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>Hoberman 2021 (doi:10.1056/nejmoa2027278) y AAO-HNSF 2022 (doi:10.1177/01945998211065662): criterios de OMA recurrente</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Hoberman 2021 (doi:10.1056/nejmoa2027278) y AAO-HNSF 2022 (doi:10.1177/01945998211065662): criterios de OMA recurrente</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -7284,17 +8220,29 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Navarro: La AAP recomienda no usar profilaxis antibiótica para reducir la frecuencia de OMA recurrente.</t>
+          <t>Navarro: La profilaxis antibiótica prolongada reduce los episodios solo mientras se toma, y a cambio favorece la resistencia; no se recomienda de rutina. En la OMA recurrente se valora primero la prevención y, si cumple criterios, los tubos de ventilación.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>AAP 2013, guía de otitis media aguda</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>Leach 2006, Cochrane (doi:10.1002/14651858.cd004401.pub2): la profilaxis prolongada reduce los episodios mientras se toma; no se encontró la recomendación de la AAP que citaba el comentario</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Solo el comentario: Leach 2006, Cochrane (doi:10.1002/14651858.cd004401.pub2): la profilaxis prolongada reduce los episodios mientras se toma; no se encontró la recomendación de la AAP que citaba el comentario Aplicada el 2026-10-13.</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N9"/>
@@ -7455,9 +8403,21 @@
           <t>Manejo de la anemia ferropénica (hierro oral como tratamiento de elección, carta del mismo mazo)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Baker, Pediatrics 2010 (doi:10.1542/peds.2010-2576) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -7504,12 +8464,24 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Mecanismo de inhibición de la absorción de hierro no hem por calcio y caseína</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Gallahan 2024 (doi:10.3390/nu16223834): la leche de vaca sin modificar reduce la absorción de hierro</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Gallahan 2024 (doi:10.3390/nu16223834): la leche de vaca sin modificar reduce la absorción de hierro</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -7556,12 +8528,24 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>AAP / AAFP, prevención de la ferropenia en lactantes</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>Zipper 2025 (doi:10.1182/blood-2025-2903): el exceso de leche de vaca es causa principal de anemia ferropénica grave; Baker 2010 localizada</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Zipper 2025 (doi:10.1182/blood-2025-2903): el exceso de leche de vaca es causa principal de anemia ferropénica grave; Baker 2010 localizada</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -7611,9 +8595,21 @@
           <t>Duración del tratamiento con hierro (carta del mismo mazo)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Baker, Pediatrics 2010 localizada, sin texto sobre la duración</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -7663,9 +8659,21 @@
           <t>AAP, Red Book 2021 (Parvovirus B19)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Broliden 2006 (doi:10.1111/j.1365-2796.2006.01697.x): cuadro leve y autolimitado en el niño inmunocompetente; sin texto sobre la exclusión escolar</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -7715,9 +8723,21 @@
           <t>AAP, Red Book 2021 (Parvovirus B19)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Broliden 2006: citopenias graves en inmunodeprimidos; sin texto sobre la inmunoglobulina</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -7767,9 +8787,21 @@
           <t>AAP, Red Book 2021 (Measles); CDC Pink Book</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>D'Souza 2001, Cochrane (doi:10.1002/14651858.cd001479): vitamina A como tratamiento de sostén; no se localizó una fuente sobre ribavirina</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -7819,9 +8851,21 @@
           <t>CDC/ACIP, Prevention of Measles, Rubella, CRS, and Mumps (MMWR 2013)</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Matysiak-Klose 2018 (doi:10.1016/j.vaccine.2018.10.070): inmunoglobulina preferentemente dentro de 6 días; la ventana de 72 h para la vacuna no se leyó en una fuente</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -7868,12 +8912,24 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>OMS, Guidelines for Measles Management; AAP, Red Book 2021</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>D'Souza 2001 y Fawzi 1993 (doi:10.1001/jama.269.7.898): dos dosis de 200 000 UI reducen la mortalidad; todo paciente con sarampión, con o sin déficit</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>D'Souza 2001 y Fawzi 1993 (doi:10.1001/jama.269.7.898): dos dosis de 200 000 UI reducen la mortalidad; todo paciente con sarampión, con o sin déficit</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -7991,9 +9047,21 @@
           <t>AAP, Red Book 2021 (Rubella)</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Principio antiviral: el aciclovir no actúa sobre el Rubivirus; sin fuente específica</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -8040,12 +9108,24 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>OMS, The treatment of diarrhoea (manual)</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -8092,12 +9172,24 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>OMS, The treatment of diarrhoea (manual)</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -8144,12 +9236,24 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>OMS, The treatment of diarrhoea (manual)</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -8264,12 +9368,24 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>ESPGHAN/ESPID, Guidelines for Acute Gastroenteritis in Children (2014); OMS</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -8316,12 +9432,24 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>ESPGHAN/ESPID, Guidelines for Acute Gastroenteritis in Children (2014); OMS</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -8368,12 +9496,24 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>OMS, The treatment of diarrhoea (manual)</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -8420,12 +9560,24 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>OMS, The treatment of diarrhoea (manual)</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -8472,12 +9624,24 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>OMS, The treatment of diarrhoea (manual)</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -8592,12 +9756,24 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>ESPGHAN/ESPID, Guidelines for Acute Gastroenteritis in Children (2014); OMS</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -8644,12 +9820,24 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>ESPGHAN/ESPID, Guidelines for Acute Gastroenteritis in Children (2014); OMS</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>ESPGHAN/ESPID 2014 (doi:10.1097/mpg.0000000000000375): rehidratación oral hipoosmolar, alimentación sin cambios, antibióticos solo en casos excepcionales; la vía enteral es superior a la intravenosa</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -8699,9 +9887,21 @@
           <t>GH Research Society, Consensus Guidelines for Diagnosis and Treatment of GH Deficiency (2000)</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Principio clínico: la talla baja familiar es una variante normal; sin fuente específica</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -8751,9 +9951,21 @@
           <t>OMS, Child Growth Standards (2006)</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>OMS: patrón de crecimiento para &lt;5 años; la literatura discute estándares nacionales (Christesen 2016, doi:10.1371/journal.pone.0157277)</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -8803,9 +10015,21 @@
           <t>OMS, Child Growth Standards (2006)</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Definición estándar de desnutrición crónica (talla para edad)</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -8852,12 +10076,24 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>OMS, Child Growth Standards (2006)</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>Christesen 2016 (doi:10.1371/journal.pone.0157277): el umbral clínico de talla baja es -2 DE</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Christesen 2016 (doi:10.1371/journal.pone.0157277): el umbral clínico de talla baja es -2 DE</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -8972,12 +10208,24 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>AHA/AAP, Neonatal Resuscitation Program, 8a ed. (2021)</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>Sankaran 2025 (doi:10.1159/000549372): la reanimación del recién nacido inicia con 21 % de oxígeno y se titula; Wang 2008 matiza a los prematuros</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Sankaran 2025 (doi:10.1159/000549372): la reanimación del recién nacido inicia con 21 % de oxígeno y se titula; Wang 2008 matiza a los prematuros</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -9160,12 +10408,24 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>AAP, Identification, Evaluation, and Management of Children with ASD (2020)</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>Sturner 2022 (doi:10.1186/s13229-021-00480-4): el tamizaje de autismo se recomienda a los 18 y 24 meses</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Sturner 2022 (doi:10.1186/s13229-021-00480-4): el tamizaje de autismo se recomienda a los 18 y 24 meses</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -9212,12 +10472,24 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>AAP, Promoting Optimal Development: Identifying Infants and Young Children with Developmental Disorders (2020)</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>Lipkin 2019, AAP (doi:10.1542/peds.2019-3449): vigilancia en cada visita y tamizaje estandarizado a edades fijas</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Lipkin 2019, AAP (doi:10.1542/peds.2019-3449): vigilancia en cada visita y tamizaje estandarizado a edades fijas</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -9267,9 +10539,21 @@
           <t>CDC, Developmental Milestones (2022)</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Hito del desarrollo estándar (CDC); sin texto localizado</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -9319,9 +10603,21 @@
           <t>AAP, Clinical Report: Hypertrophic Pyloric Stenosis; Hernanz-Schulman, Radiology (2003)</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Spicer 1982 (doi:10.1002/bjs.1800690304): la cirugía sustituyó al tratamiento médico</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -9439,9 +10735,21 @@
           <t>Canadian Paediatric Society, Position statement: Croup (2017)</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Bjornson 2004 (doi:10.1056/nejmoa033534) respalda el crup como diagnóstico clínico viral tratado con corticoide; la guía de antibióticos y radiografía no se localizó</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -9488,12 +10796,24 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Canadian Paediatric Society, Position statement: Croup (2017); Cochrane, Glucocorticoids for croup</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>Bjornson 2004 (doi:10.1056/nejmoa033534): la dexametasona reduce las consultas de retorno incluso en el crup leve</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Bjornson 2004 (doi:10.1056/nejmoa033534): la dexametasona reduce las consultas de retorno incluso en el crup leve</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -9543,9 +10863,21 @@
           <t>Canadian Paediatric Society, Position statement: Croup (2017)</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Bjornson 2004 (doi:10.1056/nejmoa033534) respalda el crup como diagnóstico clínico viral tratado con corticoide; la guía de antibióticos y radiografía no se localizó</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -9592,12 +10924,24 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>IDSA/PIDS, Guías de NAC pediátrica (Bradley et al., Clin Infect Dis 2011)</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>Bradley 2011 (doi:10.1093/cid/cir531) y Ambroggio 2023 (doi:10.1093/cid/ciad385): la guía enfatiza aminopenicilinas</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Bradley 2011 (doi:10.1093/cid/cir531) y Ambroggio 2023 (doi:10.1093/cid/ciad385): la guía enfatiza aminopenicilinas</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -9644,12 +10988,24 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>IDSA/PIDS, Guías de NAC pediátrica (Bradley et al., Clin Infect Dis 2011)</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>Ambroggio 2023: la guía IDSA/PIDS restó énfasis a la radiografía y al hemocultivo en pacientes ambulatorios</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Ambroggio 2023: la guía IDSA/PIDS restó énfasis a la radiografía y al hemocultivo en pacientes ambulatorios</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -9696,12 +11052,24 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>IDSA/PIDS, Guías de NAC pediátrica (Bradley et al., Clin Infect Dis 2011)</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>Ambroggio 2023: la guía IDSA/PIDS restó énfasis a la radiografía y al hemocultivo en pacientes ambulatorios</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Ambroggio 2023: la guía IDSA/PIDS restó énfasis a la radiografía y al hemocultivo en pacientes ambulatorios</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -9751,9 +11119,21 @@
           <t>Elección de prueba estadística por tipo de variable (cartas t de Student y Chi-Cuadrada del mismo mazo)</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Definiciones estándar de bioestadística</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -9803,9 +11183,21 @@
           <t>ASA Statement on Statistical Significance and P-Values (2016)</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Definiciones estándar de bioestadística</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -9855,9 +11247,21 @@
           <t>Definición de poder estadístico</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Definiciones estándar de bioestadística</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -9907,9 +11311,21 @@
           <t>Clasificación de pruebas paramétricas y no paramétricas</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Definiciones estándar de bioestadística</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -9959,9 +11375,21 @@
           <t>Altman DG, Practical Statistics for Medical Research (1991)</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Definiciones estándar de bioestadística</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -10011,9 +11439,21 @@
           <t>Altman DG, Practical Statistics for Medical Research (1991)</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Definiciones estándar de bioestadística</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -10063,9 +11503,21 @@
           <t>CDC/ACIP, General Best Practice Guidelines for Immunization; OMS</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Principio estándar de vacunación (esquemas retrasados no se reinician); sin fuente específica localizada</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -10112,12 +11564,24 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>CDC/ACIP, General Best Practice Guidelines for Immunization</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
+          <t>Kirtland 2019 (doi:10.1016/j.vaccine.2019.09.058) y Zimmermann 2020 (doi:10.1136/archdischild-2020-320091): vacunas vivas el mismo día o con 24-28 días de separación</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Kirtland 2019 (doi:10.1016/j.vaccine.2019.09.058) y Zimmermann 2020 (doi:10.1136/archdischild-2020-320091): vacunas vivas el mismo día o con 24-28 días de separación</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N51"/>
@@ -10275,12 +11739,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Assessment and Treatment of Patients with Suicidal Behaviors (2010)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Bryan 2017 (doi:10.1016/j.jad.2017.01.028) y Kroll 2000 (doi:10.1176/appi.ajp.157.10.1684): sin datos de eficacia de los contratos; el plan de crisis es superior</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Bryan 2017 (doi:10.1016/j.jad.2017.01.028) y Kroll 2000 (doi:10.1176/appi.ajp.157.10.1684): sin datos de eficacia de los contratos; el plan de crisis es superior</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -10327,12 +11803,24 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Assessment and Treatment of Patients with Suicidal Behaviors (2010); OMS mhGAP</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Dazzi 2014 (doi:10.1017/s0033291714001299) y Blades 2018 (doi:10.1016/j.cpr.2018.07.001): preguntar por suicidio no lo induce</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Dazzi 2014 (doi:10.1017/s0033291714001299) y Blades 2018 (doi:10.1016/j.cpr.2018.07.001): preguntar por suicidio no lo induce</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -10583,12 +12071,24 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>CANMAT/ISBD, Guidelines for the Management of Patients with Bipolar Disorder (2018)</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>Pack 2024, AAN/AES/SMFM (doi:10.1212/wnl.0000000000209279): evitar el valproato en personas con potencial de embarazo</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Pack 2024, AAN/AES/SMFM (doi:10.1212/wnl.0000000000209279): evitar el valproato en personas con potencial de embarazo</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -10635,12 +12135,24 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>CANMAT/ISBD, Guidelines for the Management of Patients with Bipolar Disorder (2018)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>Müller-Oerlinghausen 1999 (doi:10.2165/00023210-199911010-00004): los AINE y las tiazidas reducen la depuración renal de litio</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Müller-Oerlinghausen 1999 (doi:10.2165/00023210-199911010-00004): los AINE y las tiazidas reducen la depuración renal de litio</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -10758,9 +12270,21 @@
           <t>Strawn et al., Neuroleptic malignant syndrome. Am J Psychiatry (2007)</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Pileggi 2016 (doi:10.1177/1060028016657553): el tratamiento es suspender el antipsicótico, enfriar y dar soporte; sin texto sobre antipiréticos</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -10807,12 +12331,24 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Treatment of Patients with Schizophrenia (2020); NICE CG178</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>Agid 2024 (doi:10.1016/j.euroneuro.2024.04.012): la clozapina se reserva para esquizofrenia resistente tras dos antipsicóticos</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Agid 2024 (doi:10.1016/j.euroneuro.2024.04.012): la clozapina se reserva para esquizofrenia resistente tras dos antipsicóticos</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -10859,12 +12395,24 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>APA, Practice Guideline for the Treatment of Patients with Schizophrenia (2020)</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>Kishi 2026 (doi:10.1016/j.euroneuro.2026.112828): mantener el antipsicótico reduce la recaída hasta 24 meses (RR 0.45)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Kishi 2026 (doi:10.1016/j.euroneuro.2026.112828): mantener el antipsicótico reduce la recaída hasta 24 meses (RR 0.45)</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -15913,9 +17461,21 @@
           <t>CEBM Oxford, SpPin and SnNout; propiedades intrínsecas de la prueba</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Definición de libro de texto (bioestadística)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -15965,9 +17525,21 @@
           <t>Definiciones estándar de exactitud diagnóstica</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Definición de libro de texto (bioestadística)</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -16017,9 +17589,21 @@
           <t>CEBM Oxford, SpPin and SnNout</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Definición de libro de texto (bioestadística)</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -16069,9 +17653,21 @@
           <t>Interpretación de razones de verosimilitud (LR = 1: sin cambio en la probabilidad)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Definición de libro de texto (bioestadística)</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -16121,9 +17717,21 @@
           <t>Definición de la curva ROC (ya presente en la carta c_8 del mismo mazo)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Definición de libro de texto (bioestadística)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -16173,9 +17781,21 @@
           <t>CEBM Oxford; principio de pruebas de tamizaje (minimizar falsos negativos)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Definición de libro de texto (bioestadística)</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Texto estándar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N7"/>
@@ -16532,9 +18152,21 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>ACC/AHA y ESC STEMI localizadas, sin texto: dosis de carga estándar</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -16584,9 +18216,21 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>ACC/AHA y ESC STEMI localizadas, sin texto</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -16636,9 +18280,21 @@
           <t>ACC/AHA, Guideline for the Management of STEMI (2013); ESC STEMI Guidelines (2017)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>ACC/AHA y ESC STEMI localizadas, sin texto</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -16864,12 +18520,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>WSES, Jerusalem Guidelines for Diagnosis and Treatment of Acute Appendicitis (2020)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>WSES 2020 (doi:10.1186/s13017-020-00306-3): se recomienda no dar antibióticos posoperatorios en la apendicitis no complicada (1A)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2020 (doi:10.1186/s13017-020-00306-3): se recomienda no dar antibióticos posoperatorios en la apendicitis no complicada (1A)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -16919,9 +18587,21 @@
           <t>WSES, Jerusalem Guidelines for Diagnosis and Treatment of Acute Appendicitis (2020)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Poonai 2014 (doi:10.1111/acem.12509): sin aumento de perforación ni absceso con opioides en niños; evidencia de calidad baja y solo pediátrica</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -16968,12 +18648,24 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>WSES, Jerusalem Guidelines for Diagnosis and Treatment of Acute Appendicitis (2020)</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>WSES 2020: el apéndice no visualizado es frecuente (34-71 %) y se sigue con RM/TC</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2020: el apéndice no visualizado es frecuente (34-71 %) y se sigue con RM/TC</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -17020,12 +18712,24 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>WSES, Jerusalem Guidelines for Diagnosis and Treatment of Acute Appendicitis (2020)</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>WSES 2020: una dosis preoperatoria de antibiótico de amplio espectro en toda apendicectomía</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2020: una dosis preoperatoria de antibiótico de amplio espectro en toda apendicectomía</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -17072,12 +18776,24 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>WSES, Jerusalem Guidelines for Diagnosis and Treatment of Acute Appendicitis (2020)</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>WSES 2020 (doi:10.1186/s13017-020-00306-3): se recomienda no dar antibióticos posoperatorios en la apendicitis no complicada (1A)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2020 (doi:10.1186/s13017-020-00306-3): se recomienda no dar antibióticos posoperatorios en la apendicitis no complicada (1A)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -17127,9 +18843,21 @@
           <t>WSES, Jerusalem Guidelines for Diagnosis and Treatment of Acute Appendicitis (2020)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Poonai 2014 (doi:10.1111/acem.12509): sin aumento de perforación ni absceso con opioides en niños; evidencia de calidad baja y solo pediátrica</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -17176,12 +18904,24 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>WSES, Jerusalem Guidelines for Diagnosis and Treatment of Acute Appendicitis (2020)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>WSES 2020: el apéndice no visualizado es frecuente (34-71 %) y se sigue con RM/TC</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2020: el apéndice no visualizado es frecuente (34-71 %) y se sigue con RM/TC</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -17228,12 +18968,24 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>WSES, Jerusalem Guidelines for Diagnosis and Treatment of Acute Appendicitis (2020)</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>WSES 2020: una dosis preoperatoria de antibiótico de amplio espectro en toda apendicectomía</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2020: una dosis preoperatoria de antibiótico de amplio espectro en toda apendicectomía</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -17419,9 +19171,21 @@
           <t>ATLS 10a ed., Capítulo 3 y 4 (diagnóstico diferencial del choque obstructivo)</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>ATLS no está indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -17675,9 +19439,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>TG18 localizada (doi:10.1002/jhbp.509), texto no disponible para esta afirmación</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -17931,9 +19707,21 @@
           <t>Tokyo Guidelines 2018 for Acute Cholangitis and Cholecystitis</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>TG18 localizada (doi:10.1002/jhbp.509), texto no disponible para esta afirmación</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -17980,12 +19768,24 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>WSES, Management of Adhesive Small Bowel Obstruction Guidelines (2017)</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>Walshaw 2025 (doi:10.1093/bjs/znaf104): el manejo no quirúrgico tiene éxito en &gt;70 % y los retrasos &gt;72 h aumentan la morbilidad</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Walshaw 2025 (doi:10.1093/bjs/znaf104): el manejo no quirúrgico tiene éxito en &gt;70 % y los retrasos &gt;72 h aumentan la morbilidad</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -18027,17 +19827,29 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>El contraste hidrosoluble oral ayuda a predecir la resolución y también facilita el paso del contenido. Se usa como prueba diagnóstica y terapéutica.</t>
+          <t>El contraste hidrosoluble oral no está contraindicado en la obstrucción por bridas sin signos de isquemia. Sirve para estratificar (si llega al colon predice resolución), aunque su efecto terapéutico es discutido.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>WSES, Management of Adhesive Small Bowel Obstruction Guidelines (2017)</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>el efecto terapéutico del contraste es discutido (Scotté 2017, doi:10.1016/j.surg.2016.11.026); su valor predictivo es moderado (Walshaw 2025)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Solo el comentario: el efecto terapéutico del contraste es discutido (Scotté 2017, doi:10.1016/j.surg.2016.11.026); su valor predictivo es moderado (Walshaw 2025) Aplicada el 2026-10-13.</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -18152,12 +19964,24 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>WSES, Management of Adhesive Small Bowel Obstruction Guidelines (2017)</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>Walshaw 2025: descompresión nasogástrica, reposición hidroelectrolítica y ayuno en el manejo inicial</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Walshaw 2025: descompresión nasogástrica, reposición hidroelectrolítica y ayuno en el manejo inicial</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -18335,17 +20159,29 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>El ácido tranexámico se da en las primeras 3 horas. Pasado ese plazo no ayuda y puede aumentar el riesgo de trombosis.</t>
+          <t>El ácido tranexámico se da lo antes posible y dentro de las primeras 3 horas. Después de 3 horas no ayuda y puede aumentar la muerte por sangrado.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>ACS, ATLS 10a ed. (2018); CRASH-2 Collaborators, Lancet (2010)</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>CRASH-2 exploratorio (Lancet 2011, doi:10.1016/S0140-6736(11)60278-X): después de 3 h, RR 1.44 de muerte por sangrado; no se describe riesgo de trombosis</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Solo el comentario: CRASH-2 exploratorio (Lancet 2011, doi:10.1016/S0140-6736(11)60278-X): después de 3 h, RR 1.44 de muerte por sangrado; no se describe riesgo de trombosis Aplicada el 2026-10-13.</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -18395,9 +20231,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulo 3</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>ATLS (tríada letal) no indexado</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -18651,9 +20499,21 @@
           <t>ACS, ATLS 10a ed. (2018), Capítulos 3 y 4</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>ATLS no está indexado en PubMed</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N32"/>
@@ -18811,12 +20671,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>AAD, Guidelines of care for the management of acne vulgaris (2016)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>AAD 2024 (doi:10.1016/j.jaad.2023.12.017): limitar los antibióticos sistémicos y combinarlos con tratamiento tópico; isotretinoína para acné grave o refractario</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>AAD 2024 (doi:10.1016/j.jaad.2023.12.017): limitar los antibióticos sistémicos y combinarlos con tratamiento tópico; isotretinoína para acné grave o refractario</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -18863,12 +20735,24 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>AAD, Guidelines of care for the management of acne vulgaris (2016)</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>AAD 2024 (doi:10.1016/j.jaad.2023.12.017): limitar los antibióticos sistémicos y combinarlos con tratamiento tópico; isotretinoína para acné grave o refractario</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>AAD 2024 (doi:10.1016/j.jaad.2023.12.017): limitar los antibióticos sistémicos y combinarlos con tratamiento tópico; isotretinoína para acné grave o refractario</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N3"/>
@@ -19026,12 +20910,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ADA, Hyperglycemic Crises in Adults with Diabetes: A Consensus Report (2024)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Duhon 2013 (doi:10.1345/aph.1s014) y Wu 2026 (doi:10.1097/md.0000000000047529): la guía reserva el bicarbonato para pH &lt;6.9</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Duhon 2013 (doi:10.1345/aph.1s014) y Wu 2026 (doi:10.1097/md.0000000000047529): la guía reserva el bicarbonato para pH &lt;6.9</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -19149,9 +21045,21 @@
           <t>ADA, Hyperglycemic Crises in Adults with Diabetes: A Consensus Report (2024)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>JBDS localizada; el texto no menciona la concentración de la solución salina</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -19198,12 +21106,24 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ADA, Hyperglycemic Crises in Adults with Diabetes: A Consensus Report (2024)</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>JBDS (guía británica de CAD): insulina IV a ritmo fijo hasta resolver la cetosis</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>JBDS (guía británica de CAD): insulina IV a ritmo fijo hasta resolver la cetosis</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N5"/>
@@ -19361,12 +21281,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ASCRS, Clinical Practice Guidelines for Left-Sided Colonic Diverticulitis (2020)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Cirocchi 2023 (doi:10.3390/jcm12175522) y Peery, BMJ 2021 (doi:10.1136/bmj.n72): drenaje percutáneo según tamaño; cirugía ante contaminación peritoneal</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Cirocchi 2023 (doi:10.3390/jcm12175522) y Peery, BMJ 2021 (doi:10.1136/bmj.n72): drenaje percutáneo según tamaño; cirugía ante contaminación peritoneal</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -19484,9 +21416,21 @@
           <t>ASCRS, Clinical Practice Guidelines for Left-Sided Colonic Diverticulitis (2020)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Peery, BMJ 2021: la imagen determina la gravedad (no detalla la radiografía simple)</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -19533,12 +21477,24 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>ASCRS, Clinical Practice Guidelines for Left-Sided Colonic Diverticulitis (2020)</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>Peery, BMJ 2021 (doi:10.1136/bmj.n72): colonoscopia a las 6-8 semanas</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Peery, BMJ 2021 (doi:10.1136/bmj.n72): colonoscopia a las 6-8 semanas</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -19789,12 +21745,24 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>ESVS, Guidelines on the Management of Diseases of Mesenteric Arteries (2017)</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>WSES 2022 (doi:10.1186/s13017-022-00443-x): una radiografía negativa no excluye isquemia mesentérica; la angio-TC es el estudio diagnóstico</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>WSES 2022 (doi:10.1186/s13017-022-00443-x): una radiografía negativa no excluye isquemia mesentérica; la angio-TC es el estudio diagnóstico</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -19909,12 +21877,24 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>AASLD Guidance on Portal Hypertensive Bleeding (2017)</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>Baveno VII (doi:10.1016/j.jhep.2021.12.022) 6.5: vasoactivos lo antes posible; el balón es un rescate</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Baveno VII (doi:10.1016/j.jhep.2021.12.022) 6.5: vasoactivos lo antes posible; el balón es un rescate</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -20140,12 +22120,24 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ACR, BI-RADS Atlas 5a ed.; NCCN, Breast Cancer Screening and Diagnosis</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>CNGOF 2016 (doi:10.1016/j.ejogrb.2016.02.017): biopsia percutánea para BI-RADS 4-5 (grado B)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>CNGOF 2016 (doi:10.1016/j.ejogrb.2016.02.017): biopsia percutánea para BI-RADS 4-5 (grado B)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -20192,12 +22184,24 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>ACR, Appropriateness Criteria: Palpable Breast Masses</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>ACR Appropriateness Criteria, masas palpables (doi:10.1016/j.jacr.2017.02.033): diagnóstico por imagen y biopsia si hay hallazgo sospechoso</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>ACR Appropriateness Criteria, masas palpables (doi:10.1016/j.jacr.2017.02.033): diagnóstico por imagen y biopsia si hay hallazgo sospechoso</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -20247,9 +22251,21 @@
           <t>Eficacia preventiva de la vacuna en población sin VPH previo</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Principio de prevención primaria; no se localizó una guía específica</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -20299,9 +22315,21 @@
           <t>ASCCP 2019, guías de manejo</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>ASCCP 2019 (doi:10.1097/lgt.0000000000000525) localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -20343,17 +22371,29 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Castillo: El tamizaje con citología inicia a los 25 años; iniciar antes aumenta tratamientos innecesarios de lesiones que suelen regresar.</t>
+          <t>Castillo: El tamizaje con citología no es anual ni empieza a los 18 años: las guías lo inician entre los 21 y los 25 años (en México, a los 25). Antes aumenta los tratamientos innecesarios de lesiones que suelen regresar.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>NOM-014 y la carta de citología del mismo mazo</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>las guías inician entre los 21 años (USPSTF 2018) y los 25 (ACS 2020), nunca a los 18, y no es anual</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Corregir</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Solo el comentario: las guías inician entre los 21 años (USPSTF 2018) y los 25 (ACS 2020), nunca a los 18, y no es anual Aplicada el 2026-10-13.</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -20403,9 +22443,21 @@
           <t>ASCCP; manejo de citología anormal en el embarazo</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>ASCCP 2019 localizada, sin texto</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -20452,12 +22504,24 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>CDC, Sexually Transmitted Infections Treatment Guidelines 2021 (Bacterial vaginosis)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>CDC ITS 2021 (doi:10.15585/mmwr.rr7004a1): pareja masculina sin beneficio; solo azoles tópicos 7 días en el embarazo; la VB se diagnostica con Amsel o Nugent</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>CDC ITS 2021 (doi:10.15585/mmwr.rr7004a1): pareja masculina sin beneficio; solo azoles tópicos 7 días en el embarazo; la VB se diagnostica con Amsel o Nugent</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -20504,12 +22568,24 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>CDC, Sexually Transmitted Infections Treatment Guidelines 2021 (Vulvovaginal candidiasis)</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>CDC ITS 2021 (doi:10.15585/mmwr.rr7004a1): pareja masculina sin beneficio; solo azoles tópicos 7 días en el embarazo; la VB se diagnostica con Amsel o Nugent</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>CDC ITS 2021 (doi:10.15585/mmwr.rr7004a1): pareja masculina sin beneficio; solo azoles tópicos 7 días en el embarazo; la VB se diagnostica con Amsel o Nugent</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -20556,12 +22632,24 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>CDC, Sexually Transmitted Infections Treatment Guidelines 2021 (Bacterial vaginosis)</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>CDC ITS 2021 (doi:10.15585/mmwr.rr7004a1): pareja masculina sin beneficio; solo azoles tópicos 7 días en el embarazo; la VB se diagnostica con Amsel o Nugent</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Aprobar</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>CDC ITS 2021 (doi:10.15585/mmwr.rr7004a1): pareja masculina sin beneficio; solo azoles tópicos 7 días en el embarazo; la VB se diagnostica con Amsel o Nugent</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N10"/>
